--- a/papers/advisor_package/Invisible_Ledger_Data_Package_2026-09-14.xlsx
+++ b/papers/advisor_package/Invisible_Ledger_Data_Package_2026-09-14.xlsx
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>1.416208</t>
+          <t>1.445087</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>20.575429</t>
+          <t>20.568991</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>98.46</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>98.488755</t>
+          <t>98.457943</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>203.522047</t>
+          <t>203.58</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>1085.4079530000001</t>
+          <t>1085.3500000000001</t>
         </is>
       </c>
     </row>
@@ -6042,12 +6042,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>1.4162083914689871</t>
+          <t>1.4450867052023142</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>20.57542885390866</t>
+          <t>20.56899099079088</t>
         </is>
       </c>
     </row>
